--- a/T41_V012_Files/T41_V012_BOMs/Source Files/T41_RF_Board_BOM_V012.8_09-26-26.xlsx
+++ b/T41_V012_Files/T41_V012_BOMs/Source Files/T41_RF_Board_BOM_V012.8_09-26-26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bill\Documents\GitHub\T41\T41_V012_Files\T41_V012_BOMs\Source Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47E66E60-22C6-451B-98C8-96F2E0F667F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD08A65-C7EF-47A8-AE7C-862CD26F4E3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="743" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -776,9 +776,6 @@
     <t>584-AD8599ARZ-R</t>
   </si>
   <si>
-    <t>652-CR1206FX-2701ELF</t>
-  </si>
-  <si>
     <t>TP1, TP2, TP3, TP4, TP5, TP6, TP7, TP8, TP9, TP10, TP11, TP12, TP13, TP14, TP17, TP18</t>
   </si>
   <si>
@@ -837,9 +834,6 @@
   </si>
   <si>
     <t>R26, R34, R49, R50, R51, R60, R61, R62, R63</t>
-  </si>
-  <si>
-    <t>71-CRCW1206J-1.1K-E3</t>
   </si>
   <si>
     <r>
@@ -921,6 +915,12 @@
   </si>
   <si>
     <t>1.6K Ohm SMD 1206 Resistor</t>
+  </si>
+  <si>
+    <t>652-CR1206FX-1601ELF</t>
+  </si>
+  <si>
+    <t>652-CR1206FX-1101ELF</t>
   </si>
 </sst>
 </file>
@@ -1450,7 +1450,7 @@
         <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -1534,13 +1534,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
+        <v>251</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>253</v>
-      </c>
       <c r="D5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G5" s="5">
         <v>0.13</v>
@@ -1555,13 +1555,13 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G6" s="5">
         <v>0.11</v>
@@ -1633,7 +1633,7 @@
         <v>25</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D9" t="s">
         <v>26</v>
@@ -1876,7 +1876,7 @@
         <v>67</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D17" t="s">
         <v>68</v>
@@ -2110,7 +2110,7 @@
         <v>104</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D24" t="s">
         <v>105</v>
@@ -2173,7 +2173,7 @@
         <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>114</v>
@@ -2209,7 +2209,7 @@
         <v>118</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D27" t="s">
         <v>119</v>
@@ -2239,13 +2239,13 @@
         <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D28" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="G28" s="5">
         <v>0.1</v>
@@ -2260,7 +2260,7 @@
         <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>122</v>
@@ -2293,7 +2293,7 @@
         <v>2</v>
       </c>
       <c r="B30" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>126</v>
@@ -2329,10 +2329,10 @@
         <v>130</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D31" t="s">
         <v>250</v>
-      </c>
-      <c r="D31" t="s">
-        <v>251</v>
       </c>
       <c r="G31" s="5">
         <v>2.1000000000000001E-2</v>
@@ -2392,13 +2392,13 @@
         <v>1</v>
       </c>
       <c r="B33" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>138</v>
       </c>
       <c r="D33" t="s">
-        <v>241</v>
+        <v>266</v>
       </c>
       <c r="G33" s="5">
         <v>0.1</v>
@@ -2494,7 +2494,7 @@
         <v>152</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F36" t="s">
         <v>153</v>
@@ -2974,7 +2974,7 @@
         <v>52</v>
       </c>
       <c r="F52" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G52" s="5">
         <v>0.7</v>
@@ -2989,14 +2989,14 @@
         <v>2</v>
       </c>
       <c r="B53" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>244</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>245</v>
       </c>
       <c r="D53" s="12"/>
       <c r="F53" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G53" s="5">
         <v>5.84</v>
@@ -3011,14 +3011,14 @@
         <v>1</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>216</v>
       </c>
       <c r="D54" s="12"/>
       <c r="F54" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G54" s="5">
         <v>11.74</v>
